--- a/NECP Scenario/Results/Regional Results/RODOS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/RODOS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.304421970409643E-08</v>
+        <v>4.87846475305802E-08</v>
       </c>
       <c r="C3">
-        <v>3.322366336529725E-08</v>
+        <v>4.904849254478078E-08</v>
       </c>
       <c r="D3">
-        <v>0.016944175013611</v>
+        <v>0.0199996567575881</v>
       </c>
       <c r="E3">
-        <v>0.021681664261148</v>
+        <v>0.0303091678663063</v>
       </c>
       <c r="F3">
-        <v>0.0464455099454781</v>
+        <v>0.119579640276497</v>
       </c>
       <c r="G3">
-        <v>0.1050248438295828</v>
+        <v>0.1709915645018797</v>
       </c>
       <c r="H3">
-        <v>0.1672897153223244</v>
+        <v>0.4554489771840136</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.000000000005123</v>
+        <v>2.000000000006038</v>
       </c>
       <c r="C13">
-        <v>2.000000000007158</v>
+        <v>2.000000000009029</v>
       </c>
       <c r="D13">
-        <v>2.000000000011324</v>
+        <v>2.000000000014848</v>
       </c>
       <c r="E13">
-        <v>2.000000000021006</v>
+        <v>2.000000000024982</v>
       </c>
       <c r="F13">
-        <v>2.000000000036254</v>
+        <v>2.000000000045079</v>
       </c>
       <c r="G13">
-        <v>2.00000000006717</v>
+        <v>2.000000000085014</v>
       </c>
       <c r="H13">
-        <v>2.000000000370171</v>
+        <v>2.000000000445431</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.5183818888873221</v>
+        <v>0.5187369360484189</v>
       </c>
       <c r="E27">
-        <v>0.6703594559546744</v>
+        <v>0.6703594559244576</v>
       </c>
       <c r="F27">
-        <v>0.6703594559704767</v>
+        <v>0.6703594559517621</v>
       </c>
       <c r="G27">
-        <v>0.6703594559805439</v>
+        <v>0.6703594559683659</v>
       </c>
       <c r="H27">
-        <v>0.6703594559906806</v>
+        <v>0.6703594559849114</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>8.702228505467862E-08</v>
+        <v>1.286163654408641E-07</v>
       </c>
       <c r="E29">
-        <v>0.2114705849667843</v>
+        <v>0.2114705849528389</v>
       </c>
       <c r="F29">
-        <v>0.2114705849782493</v>
+        <v>0.2114705849691865</v>
       </c>
       <c r="G29">
-        <v>0.2114705849856243</v>
+        <v>0.2114705849796553</v>
       </c>
       <c r="H29">
-        <v>0.2114705849931415</v>
+        <v>0.211470584990294</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1.403998749580573E-08</v>
+        <v>2.072808768093641E-08</v>
       </c>
       <c r="E33">
-        <v>8.394620842034218E-08</v>
+        <v>1.00233849082934E-07</v>
       </c>
       <c r="F33">
-        <v>2.776510018820556E-07</v>
+        <v>3.267017457768902E-07</v>
       </c>
       <c r="G33">
-        <v>5.639461594853204E-07</v>
+        <v>5.760414203943017E-07</v>
       </c>
       <c r="H33">
-        <v>2.338573062380144E-05</v>
+        <v>0.1510202218019954</v>
       </c>
     </row>
     <row r="34" spans="1:8">
